--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_7_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_7_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D894BC-BF97-47D4-84C3-518612229F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD54373-E196-459C-8F00-4C0D5F25AC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,34 +55,37 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT DALBHARAT 29 May 2025 2100 PE</t>
-  </si>
-  <si>
-    <t>26-05-2025</t>
-  </si>
-  <si>
-    <t>OPT ADANIENSOL 29 May 2025 880 CE</t>
-  </si>
-  <si>
-    <t>OPT IRFC 29 May 2025 140 CE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 29 May 2025 24800 PE</t>
-  </si>
-  <si>
-    <t>27-05-2025</t>
-  </si>
-  <si>
-    <t>OPT HAL 29 May 2025 5000 CE</t>
-  </si>
-  <si>
-    <t>OPT TATACONSUM 29 May 2025 1130 PE</t>
-  </si>
-  <si>
-    <t>OPT BSE 26 Jun 2025 2600 CE</t>
-  </si>
-  <si>
-    <t>30-05-2025</t>
+    <t>OPT JIOFIN 31 Jul 2025 320 CE</t>
+  </si>
+  <si>
+    <t>30-06-2025</t>
+  </si>
+  <si>
+    <t>OPT GODREJPROP 31 Jul 2025 2400 PE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 03 Jul 2025 25600 PE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 03 Jul 2025 25500 CE</t>
+  </si>
+  <si>
+    <t>01-07-2025</t>
+  </si>
+  <si>
+    <t>OPT COFORGE 31 Jul 2025 1940 CE</t>
+  </si>
+  <si>
+    <t>OPT COFORGE 31 Jul 2025 1900 CE</t>
+  </si>
+  <si>
+    <t>OPT APLAPOLLO 31 Jul 2025 1760 PE</t>
+  </si>
+  <si>
+    <t>02-07-2025</t>
+  </si>
+  <si>
+    <t>OPT NBCC 31 Jul 2025 120 PE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -435,10 +438,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -454,10 +457,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -466,10 +469,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -492,331 +495,378 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45803</v>
+        <v>45838</v>
       </c>
       <c r="D2">
-        <v>275</v>
+        <v>2350</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>18.45</v>
       </c>
       <c r="F2">
-        <v>13475</v>
+        <v>43357.5</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>275</v>
+        <v>2350</v>
       </c>
       <c r="I2">
-        <v>42.9</v>
+        <v>17.55</v>
       </c>
       <c r="J2">
-        <v>11797.5</v>
+        <v>41242.5</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>-1677.5</v>
+        <v>-2115</v>
       </c>
       <c r="M2">
-        <v>70.03</v>
+        <v>124.66</v>
       </c>
       <c r="N2">
-        <v>-1747.53</v>
+        <v>-2239.66</v>
       </c>
       <c r="O2">
-        <v>1677.5</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45803</v>
+        <v>45838</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>275</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>116.4</v>
       </c>
       <c r="F3">
-        <v>11875</v>
+        <v>32010</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3">
-        <v>625</v>
+        <v>275</v>
       </c>
       <c r="I3">
-        <v>19.8</v>
+        <v>112</v>
       </c>
       <c r="J3">
-        <v>12375</v>
+        <v>30800</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>500</v>
+        <v>-1210</v>
       </c>
       <c r="M3">
-        <v>70.38</v>
+        <v>105.37</v>
       </c>
       <c r="N3">
-        <v>429.62</v>
+        <v>-1315.37</v>
       </c>
       <c r="O3">
-        <v>500</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45803</v>
+        <v>45838</v>
       </c>
       <c r="D4">
-        <v>3525</v>
+        <v>300</v>
       </c>
       <c r="E4">
-        <v>2.4</v>
+        <v>129</v>
       </c>
       <c r="F4">
-        <v>8460</v>
+        <v>38700</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H4">
-        <v>3525</v>
+        <v>300</v>
       </c>
       <c r="I4">
-        <v>2.15</v>
+        <v>133.97999999999999</v>
       </c>
       <c r="J4">
-        <v>7578.75</v>
+        <v>40192.5</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>-881.25</v>
+        <v>1492.5</v>
       </c>
       <c r="M4">
-        <v>61.77</v>
+        <v>216.12</v>
       </c>
       <c r="N4">
-        <v>-943.02</v>
+        <v>1276.3800000000001</v>
       </c>
       <c r="O4">
-        <v>881.25</v>
+        <v>1492.5</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>45804</v>
+        <v>45839</v>
       </c>
       <c r="D5">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="E5">
-        <v>212.55</v>
+        <v>127.85</v>
       </c>
       <c r="F5">
-        <v>15941.25</v>
+        <v>38355</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H5">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="I5">
-        <v>220.6</v>
+        <v>121.08</v>
       </c>
       <c r="J5">
-        <v>16545</v>
+        <v>36322.5</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>603.75</v>
+        <v>-2032.5</v>
       </c>
       <c r="M5">
-        <v>77.89</v>
+        <v>163.27000000000001</v>
       </c>
       <c r="N5">
-        <v>525.86</v>
+        <v>-2195.77</v>
       </c>
       <c r="O5">
-        <v>603.75</v>
+        <v>2032.5</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>45804</v>
+        <v>45839</v>
       </c>
       <c r="D6">
-        <v>150</v>
+        <v>375</v>
       </c>
       <c r="E6">
-        <v>116.35</v>
+        <v>88.8</v>
       </c>
       <c r="F6">
-        <v>17452.5</v>
+        <v>33300</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H6">
-        <v>150</v>
+        <v>375</v>
       </c>
       <c r="I6">
-        <v>120.25</v>
+        <v>88.85</v>
       </c>
       <c r="J6">
-        <v>18037.5</v>
+        <v>33318.75</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>585</v>
+        <v>18.75</v>
       </c>
       <c r="M6">
-        <v>80.959999999999994</v>
+        <v>109.53</v>
       </c>
       <c r="N6">
-        <v>504.04</v>
+        <v>-90.78</v>
       </c>
       <c r="O6">
-        <v>585</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>258</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>45804</v>
+        <v>45839</v>
       </c>
       <c r="D7">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="E7">
-        <v>13.05</v>
+        <v>103.3</v>
       </c>
       <c r="F7">
-        <v>5950.8</v>
+        <v>38737.5</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H7">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="I7">
-        <v>13.05</v>
+        <v>97.25</v>
       </c>
       <c r="J7">
-        <v>5950.8</v>
+        <v>36468.75</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>-2268.75</v>
       </c>
       <c r="M7">
-        <v>58.33</v>
+        <v>116.03</v>
       </c>
       <c r="N7">
-        <v>-58.33</v>
+        <v>-2384.7800000000002</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2268.75</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>45807</v>
+        <v>45840</v>
       </c>
       <c r="D8">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="E8">
-        <v>148</v>
+        <v>53.55</v>
       </c>
       <c r="F8">
-        <v>111000</v>
+        <v>18742.5</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H8">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="I8">
-        <v>147.15</v>
+        <v>59.1</v>
       </c>
       <c r="J8">
-        <v>110362.5</v>
+        <v>20685</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>-637.5</v>
+        <v>1942.5</v>
       </c>
       <c r="M8">
-        <v>300.47000000000003</v>
+        <v>85.03</v>
       </c>
       <c r="N8">
-        <v>-937.97</v>
+        <v>1857.47</v>
       </c>
       <c r="O8">
-        <v>637.5</v>
+        <v>1942.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>182</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45840</v>
+      </c>
+      <c r="D9">
+        <v>13000</v>
+      </c>
+      <c r="E9">
+        <v>5.03</v>
+      </c>
+      <c r="F9">
+        <v>65325</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>13000</v>
+      </c>
+      <c r="I9">
+        <v>4.83</v>
+      </c>
+      <c r="J9">
+        <v>62725</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>-2600</v>
+      </c>
+      <c r="M9">
+        <v>213</v>
+      </c>
+      <c r="N9">
+        <v>-2813</v>
+      </c>
+      <c r="O9">
+        <v>2600</v>
       </c>
     </row>
   </sheetData>
